--- a/reporte_supermercados.xlsx
+++ b/reporte_supermercados.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="129">
   <si>
     <t>🛒 REPORTE RPA: COMPARADOR DE PRECIOS Y CANASTA INTELIGENTE</t>
   </si>
@@ -351,14 +351,14 @@
     <t>🎯 CONSULTA INDIVIDUAL: ¿DÓNDE TE CONVIENE COMPRAR?</t>
   </si>
   <si>
-    <t>🔎 PRODUCTO CONSULTADO:  "LECHE"</t>
-  </si>
-  <si>
-    <t>Intención detectada: GENERICA  │  Fecha: 2026-09-10  │  Supermercados relevados: Carrefour, COTO y Día %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏆 TE CONVIENE COMPRAR EN: COTO ($ 2.140,00)
-💰 AHORRO POTENCIAL: $ 200,00 (9% menos que en Carrefour)</t>
+    <t>🔎 PRODUCTO CONSULTADO:  "MAYONESA NATURA"</t>
+  </si>
+  <si>
+    <t>Intención detectada: ESPECIFICA (Marca: NATURA)  │  Fecha: 2026-09-10  │  Supermercados relevados: Carrefour, COTO y Día %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏆 TE CONVIENE COMPRAR EN: Carrefour ($ 3.039,00)
+💰 AHORRO POTENCIAL: $ 3,00 (0% menos que en COTO)</t>
   </si>
   <si>
     <t>Precio Vigente</t>
@@ -376,31 +376,28 @@
     <t>Enlace Web Directo</t>
   </si>
   <si>
+    <t>🏆 GANADOR</t>
+  </si>
+  <si>
+    <t>Mayonesa Natura 475 g.</t>
+  </si>
+  <si>
+    <t>Coincidencia específica validada (marca, categoría y atributos conformes).</t>
+  </si>
+  <si>
+    <t>🔗 Ver en Carrefour</t>
+  </si>
+  <si>
     <t xml:space="preserve"> VALIDADA</t>
   </si>
   <si>
-    <t>Leche Protein La Serenisima 1L</t>
-  </si>
-  <si>
-    <t>Coincidencia genérica validada (alternativa comercial aceptable).</t>
-  </si>
-  <si>
-    <t>🔗 Ver en Carrefour</t>
-  </si>
-  <si>
-    <t>🏆 GANADOR</t>
-  </si>
-  <si>
-    <t>Leche Multidefensas 3% LA SERENISIMA Sachet 1l</t>
+    <t>Mayonesa NATURA Pouch 475 Gr</t>
   </si>
   <si>
     <t>🔗 Ver en COTO</t>
   </si>
   <si>
-    <t>N/D</t>
-  </si>
-  <si>
-    <t>❌ NO ENCONTRADO</t>
+    <t>Mayonesa Natura 500 Ml.</t>
   </si>
   <si>
     <t>🔗 Ver en Día %</t>
@@ -416,7 +413,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -558,6 +555,29 @@
     </font>
     <font>
       <b/>
+      <color rgb="276A3C"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="276A3C"/>
+      <sz val="9.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <color rgb="FF444444"/>
+      <sz val="8.5"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF333333"/>
       <sz val="9.5"/>
       <name val="Segoe UI"/>
@@ -573,54 +593,13 @@
       <name val="Segoe UI"/>
     </font>
     <font>
-      <color rgb="FF444444"/>
-      <sz val="8.5"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="276A3C"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="276A3C"/>
-      <sz val="9.5"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF888888"/>
-      <strike/>
-      <sz val="9.5"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="C00000"/>
-      <sz val="9"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
-      <color rgb="C00000"/>
-      <sz val="8.5"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
       <i/>
       <color rgb="FF666666"/>
       <sz val="9"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,11 +646,6 @@
         <fgColor rgb="FCE4D6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9EAE1"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -700,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -821,52 +795,43 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1208,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1735,29 +1700,6 @@
         <v>91</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="H35" s="23" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1788,7 +1730,6 @@
     <hyperlink ref="H24" r:id="rId9"/>
     <hyperlink ref="H33" r:id="rId10"/>
     <hyperlink ref="H34" r:id="rId11"/>
-    <hyperlink ref="H35" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2177,7 +2118,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="43">
-        <v>2340</v>
+        <v>3039</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>119</v>
@@ -2197,7 +2138,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="49">
-        <v>2140</v>
+        <v>3042</v>
       </c>
       <c r="D12" s="50" t="s">
         <v>123</v>
@@ -2213,34 +2154,34 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="49">
+        <v>3040</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="F13" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="47" t="s">
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="54" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/reporte_supermercados.xlsx
+++ b/reporte_supermercados.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
   <si>
     <t>🛒 REPORTE RPA: COMPARADOR DE PRECIOS Y CANASTA INTELIGENTE</t>
   </si>
   <si>
-    <t>Relevamiento en tiempo real en Carrefour, COTO y Día % • Modo Compra del Mes y Búsquedas Individuales • 10/9/2026</t>
+    <t>Relevamiento en tiempo real en Carrefour, COTO y Día % • Modo Compra del Mes y Búsquedas Individuales • 11/9/2026</t>
   </si>
   <si>
     <t>🏆 SÚPER RECOMENDADO (CANASTA)</t>
@@ -33,37 +33,49 @@
     <t>💸 AHORRO MÁXIMO</t>
   </si>
   <si>
+    <t>COTO</t>
+  </si>
+  <si>
+    <t>📊 EVALUACIÓN COMPARATIVA: COSTO TOTAL DE LA CANASTA COMPLETA</t>
+  </si>
+  <si>
+    <t>Supermercado</t>
+  </si>
+  <si>
+    <t>Costo Canasta Total</t>
+  </si>
+  <si>
+    <t>Artículos Disponibles</t>
+  </si>
+  <si>
+    <t>Artículos con Problema</t>
+  </si>
+  <si>
+    <t>Precios Más Bajos Ganados</t>
+  </si>
+  <si>
+    <t>Diferencia vs Mejor</t>
+  </si>
+  <si>
+    <t>Estado / Recomendación</t>
+  </si>
+  <si>
     <t>Carrefour</t>
   </si>
   <si>
-    <t>📊 EVALUACIÓN COMPARATIVA: COSTO TOTAL DE LA CANASTA COMPLETA</t>
-  </si>
-  <si>
-    <t>Supermercado</t>
-  </si>
-  <si>
-    <t>Costo Canasta Total</t>
-  </si>
-  <si>
-    <t>Artículos Disponibles</t>
-  </si>
-  <si>
-    <t>Artículos con Problema</t>
-  </si>
-  <si>
-    <t>Precios Más Bajos Ganados</t>
-  </si>
-  <si>
-    <t>Diferencia vs Mejor</t>
-  </si>
-  <si>
-    <t>Estado / Recomendación</t>
-  </si>
-  <si>
-    <t>8 de 9</t>
-  </si>
-  <si>
-    <t>1 productos</t>
+    <t>2 de 2</t>
+  </si>
+  <si>
+    <t>0 productos</t>
+  </si>
+  <si>
+    <t>+$1.934,51</t>
+  </si>
+  <si>
+    <t>Más costoso</t>
+  </si>
+  <si>
+    <t>2 productos</t>
   </si>
   <si>
     <t>Mejor opción</t>
@@ -72,25 +84,10 @@
     <t>🏆 RECOMENDADO</t>
   </si>
   <si>
-    <t>COTO</t>
-  </si>
-  <si>
-    <t>+$26.919,49</t>
-  </si>
-  <si>
-    <t>Más costoso</t>
-  </si>
-  <si>
     <t>Día %</t>
   </si>
   <si>
-    <t>9 de 9</t>
-  </si>
-  <si>
-    <t>7 productos</t>
-  </si>
-  <si>
-    <t>+$1.446,50</t>
+    <t>+$6.023,51</t>
   </si>
   <si>
     <t>🛒 PRODUCTO GANADOR POR ARTÍCULO (MEJOR PRECIO)</t>
@@ -117,129 +114,39 @@
     <t>Enlace Directo</t>
   </si>
   <si>
-    <t>LECHE</t>
-  </si>
-  <si>
-    <t>🏆 Día %</t>
-  </si>
-  <si>
-    <t>Leche Semi Descremada DIA Larga Vida 1 Lt.</t>
-  </si>
-  <si>
-    <t>Carrefour ($2.340)</t>
-  </si>
-  <si>
-    <t>-$640</t>
+    <t>GALLETITAS</t>
+  </si>
+  <si>
+    <t>🏆 COTO</t>
+  </si>
+  <si>
+    <t>Galletitas Crackers CEREALITAS Clásicas 212g</t>
+  </si>
+  <si>
+    <t>Día % ($6.649)</t>
+  </si>
+  <si>
+    <t>-$4.619</t>
   </si>
   <si>
     <t>🔗 Ver en Tienda</t>
   </si>
   <si>
-    <t>ARROZ</t>
-  </si>
-  <si>
-    <t>Arroz Parboil Molinos Ala 1 Kg.</t>
-  </si>
-  <si>
-    <t>COTO ($1.999)</t>
-  </si>
-  <si>
-    <t>-$510,5</t>
-  </si>
-  <si>
-    <t>FIDEOS</t>
-  </si>
-  <si>
-    <t>Fideos Tirabuzon N28 Matarazzo 500 Gr.</t>
-  </si>
-  <si>
-    <t>COTO ($1.750)</t>
-  </si>
-  <si>
-    <t>-$510</t>
-  </si>
-  <si>
-    <t>ACEITE</t>
-  </si>
-  <si>
-    <t>Aceite de Girasol Dia 1,5 Lt.</t>
-  </si>
-  <si>
-    <t>COTO ($6.530)</t>
-  </si>
-  <si>
-    <t>-$1.930</t>
-  </si>
-  <si>
-    <t>YERBA</t>
-  </si>
-  <si>
-    <t>Yerba Mate Mañanita 4 Flex 1 Kg.</t>
-  </si>
-  <si>
-    <t>COTO ($5.370)</t>
-  </si>
-  <si>
-    <t>-$1.580</t>
-  </si>
-  <si>
-    <t>AZUCAR</t>
-  </si>
-  <si>
-    <t>🏆 Carrefour</t>
-  </si>
-  <si>
-    <t>Azúcar común Azucel tipo A bolsa 1 kg.</t>
-  </si>
-  <si>
-    <t>COTO ($1.567)</t>
-  </si>
-  <si>
-    <t>-$177</t>
-  </si>
-  <si>
-    <t>CAFE</t>
-  </si>
-  <si>
-    <t>Cafe Instantáneo Nescafe Dolca Mixes Caramel Doypack X 125 Gr.</t>
-  </si>
-  <si>
-    <t>COTO ($29.671)</t>
-  </si>
-  <si>
-    <t>-$26.629</t>
-  </si>
-  <si>
-    <t>GALLETITAS</t>
-  </si>
-  <si>
-    <t>🏆 COTO</t>
-  </si>
-  <si>
-    <t>Galletitas Crackers CEREALITAS Clásicas 212g</t>
-  </si>
-  <si>
-    <t>Día % ($6.649)</t>
-  </si>
-  <si>
-    <t>-$4.619</t>
-  </si>
-  <si>
     <t>PAPEL HIGIENICO</t>
   </si>
   <si>
-    <t>Papel Higiénico Doble Hoja 30mts 6 Ud.</t>
-  </si>
-  <si>
-    <t>Carrefour ($4.250)</t>
-  </si>
-  <si>
-    <t>-$1.340</t>
+    <t>Papel Higiénico HIGIENOL Plus Fusión Doble Hoja 30 M 4 Un</t>
+  </si>
+  <si>
+    <t>Día % ($4.850)</t>
+  </si>
+  <si>
+    <t>-$1.404,51</t>
   </si>
   <si>
     <t xml:space="preserve">💡 CONCLUSIÓN Y ESTRATEGIA RECOMENDADA POR EL BOT RPA:
-1. Si realizás toda la compra mensual en un único lugar: El supermercado más conveniente es Carrefour con un costo de $25.443,00.
-2. Si realizás una compra combinada (comprando cada producto en su supermercado ganador): Pagás solo $22.190,50, ahorrando un total de $30.171,99.
+1. Si realizás toda la compra mensual en un único lugar: El supermercado más conveniente es COTO con un costo de $5.475,49.
+2. Si realizás una compra combinada (comprando cada producto en su supermercado ganador): Pagás solo $5.475,49, ahorrando un total de $6.023,51.
 3. Podés verificar el detalle de stock y faltantes en la sección ubicada debajo en esta misma hoja.</t>
   </si>
   <si>
@@ -264,7 +171,7 @@
     <t>Enlace Web</t>
   </si>
   <si>
-    <t>2026-09-10</t>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>leche</t>
@@ -282,18 +189,6 @@
     <t>🔗 Ver Tienda</t>
   </si>
   <si>
-    <t>cafe</t>
-  </si>
-  <si>
-    <t>Nescafé Dolca Suave 170 grs</t>
-  </si>
-  <si>
-    <t>COINCIDENCIA NO VÁLIDA</t>
-  </si>
-  <si>
-    <t>El producto devuelto (Nescafé Dolca Suave 170 grs) no pertenece a la categoría CAFE.</t>
-  </si>
-  <si>
     <t>🛒 CANASTA MENSUAL: COMPARATIVA DETALLADA DE PRECIOS POR SUPERMERCADO</t>
   </si>
   <si>
@@ -309,56 +204,29 @@
     <t>Ahorro Máximo</t>
   </si>
   <si>
-    <t>-$640,00</t>
-  </si>
-  <si>
-    <t>-$510,50</t>
-  </si>
-  <si>
-    <t>-$510,00</t>
-  </si>
-  <si>
-    <t>-$1.930,00</t>
-  </si>
-  <si>
-    <t>-$1.580,00</t>
-  </si>
-  <si>
-    <t>-$177,00</t>
-  </si>
-  <si>
-    <t>No válida</t>
-  </si>
-  <si>
-    <t>-$26.629,00</t>
-  </si>
-  <si>
     <t>-$4.619,00</t>
   </si>
   <si>
-    <t>-$1.340,00</t>
-  </si>
-  <si>
     <t>TOTAL CANASTA</t>
   </si>
   <si>
     <t>Óptima Combinada</t>
   </si>
   <si>
-    <t>-$30.171,99</t>
+    <t>-$6.023,51</t>
   </si>
   <si>
     <t>🎯 CONSULTA INDIVIDUAL: ¿DÓNDE TE CONVIENE COMPRAR?</t>
   </si>
   <si>
-    <t>🔎 PRODUCTO CONSULTADO:  "MAYONESA NATURA"</t>
-  </si>
-  <si>
-    <t>Intención detectada: ESPECIFICA (Marca: NATURA)  │  Fecha: 2026-09-10  │  Supermercados relevados: Carrefour, COTO y Día %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🏆 TE CONVIENE COMPRAR EN: Carrefour ($ 3.039,00)
-💰 AHORRO POTENCIAL: $ 3,00 (0% menos que en COTO)</t>
+    <t>🔎 PRODUCTO CONSULTADO:  "LECHE"</t>
+  </si>
+  <si>
+    <t>Intención detectada: GENERICA  │  Fecha: 2026-09-11  │  Supermercados relevados: Carrefour, COTO y Día %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏆 TE CONVIENE COMPRAR EN: Carrefour ($ 2.340,00)
+💰 AHORRO POTENCIAL: $ 995,00 (30% menos que en Día %)</t>
   </si>
   <si>
     <t>Precio Vigente</t>
@@ -379,10 +247,10 @@
     <t>🏆 GANADOR</t>
   </si>
   <si>
-    <t>Mayonesa Natura 475 g.</t>
-  </si>
-  <si>
-    <t>Coincidencia específica validada (marca, categoría y atributos conformes).</t>
+    <t>Leche Protein La Serenisima 1L</t>
+  </si>
+  <si>
+    <t>Coincidencia genérica validada (alternativa comercial aceptable).</t>
   </si>
   <si>
     <t>🔗 Ver en Carrefour</t>
@@ -391,13 +259,10 @@
     <t xml:space="preserve"> VALIDADA</t>
   </si>
   <si>
-    <t>Mayonesa NATURA Pouch 475 Gr</t>
-  </si>
-  <si>
     <t>🔗 Ver en COTO</t>
   </si>
   <si>
-    <t>Mayonesa Natura 500 Ml.</t>
+    <t>Leche Infantil Nutrilon Profutura Etapa 1 Brick 200 Ml.</t>
   </si>
   <si>
     <t>🔗 Ver en Día %</t>
@@ -413,7 +278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -463,21 +328,17 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF333333"/>
+    </font>
+    <font>
+      <color rgb="FF666666"/>
+    </font>
+    <font>
+      <color rgb="FF777777"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="276A3C"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="C00000"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF333333"/>
-    </font>
-    <font>
-      <color rgb="FF666666"/>
-    </font>
-    <font>
-      <color rgb="FF777777"/>
     </font>
     <font>
       <b/>
@@ -507,6 +368,10 @@
     </font>
     <font>
       <b/>
+      <color rgb="C00000"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
       <name val="Segoe UI"/>
@@ -520,11 +385,6 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF888888"/>
-      <sz val="9"/>
     </font>
     <font>
       <b/>
@@ -674,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,7 +563,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -712,40 +572,37 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -758,7 +615,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -771,13 +631,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -786,52 +643,52 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1230,15 +1087,15 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">
-        <v>25443</v>
+        <v>5475.49</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6">
-        <v>22190.5</v>
+        <v>5475.49</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6">
-        <v>30171.989999999998</v>
+        <v>6023.51</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
@@ -1277,76 +1134,76 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C10" s="10">
-        <v>25443</v>
+        <v>7410</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="12">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="G10" s="12" t="s">
         <v>18</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="15">
-        <v>52362.49</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="14">
+        <v>5475.49</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="12">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="G11" s="15" t="s">
         <v>21</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="15">
-        <v>26889.5</v>
+        <v>23</v>
+      </c>
+      <c r="C12" s="10">
+        <v>11499</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E12" s="11">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>21</v>
+      <c r="H12" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1357,350 +1214,189 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="8" t="s">
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
+      <c r="C16" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="D16" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="E16" s="14">
+        <v>2030</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="10">
-        <v>1700</v>
-      </c>
-      <c r="F16" s="21" t="s">
+      <c r="G16" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="H16" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="H16" s="23" t="s">
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+      <c r="C17" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="E17" s="14">
+        <v>3445.49</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="10">
-        <v>1488.5</v>
-      </c>
-      <c r="F17" s="21" t="s">
+      <c r="G17" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="H17" s="22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="20" t="s">
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="10">
-        <v>1240</v>
-      </c>
-      <c r="F18" s="21" t="s">
+      <c r="C25" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="E25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+      <c r="F25" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="20" t="s">
+      <c r="G25" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="10">
-        <v>4600</v>
-      </c>
-      <c r="F19" s="21" t="s">
+      <c r="H25" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="22" t="s">
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
+      <c r="C26" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="20" t="s">
+      <c r="E26" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="10">
-        <v>3790</v>
-      </c>
-      <c r="F20" s="21" t="s">
+      <c r="F26" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G26" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
+      <c r="H26" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="10">
-        <v>1390</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="10">
-        <v>3042</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="10">
-        <v>2030</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="10">
-        <v>2910</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>87</v>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1715,21 +1411,14 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B26:H29"/>
-    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B19:H22"/>
+    <mergeCell ref="B24:H24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H16" r:id="rId1"/>
     <hyperlink ref="H17" r:id="rId2"/>
-    <hyperlink ref="H18" r:id="rId3"/>
-    <hyperlink ref="H19" r:id="rId4"/>
-    <hyperlink ref="H20" r:id="rId5"/>
-    <hyperlink ref="H21" r:id="rId6"/>
-    <hyperlink ref="H22" r:id="rId7"/>
-    <hyperlink ref="H23" r:id="rId8"/>
-    <hyperlink ref="H24" r:id="rId9"/>
-    <hyperlink ref="H33" r:id="rId10"/>
-    <hyperlink ref="H34" r:id="rId11"/>
+    <hyperlink ref="H26" r:id="rId3"/>
+    <hyperlink ref="H27" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1738,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1750,7 +1439,7 @@
   <sheetData>
     <row r="2" ht="34" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -1761,7 +1450,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="31" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
@@ -1772,255 +1461,94 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="32" t="s">
-        <v>19</v>
-      </c>
       <c r="E5" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="33">
+        <v>3160</v>
+      </c>
+      <c r="D6" s="14">
+        <v>2030</v>
+      </c>
+      <c r="E6" s="33">
+        <v>6649</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="33">
-        <v>2340</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="10">
-        <v>1700</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="35">
-        <v>1700</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>97</v>
+      <c r="G6" s="34">
+        <v>2030</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="33">
-        <v>1940</v>
-      </c>
-      <c r="D7" s="33">
-        <v>1999</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1488.5</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="35">
-        <v>1488.5</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="33">
-        <v>1749</v>
-      </c>
-      <c r="D8" s="33">
-        <v>1750</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1240</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="35">
-        <v>1240</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="33">
-        <v>5405</v>
-      </c>
-      <c r="D9" s="33">
-        <v>6530</v>
-      </c>
-      <c r="E9" s="10">
-        <v>4600</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="35">
-        <v>4600</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="33">
-        <v>5209</v>
-      </c>
-      <c r="D10" s="33">
-        <v>5370</v>
-      </c>
-      <c r="E10" s="10">
-        <v>3790</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="35">
-        <v>3790</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1390</v>
-      </c>
-      <c r="D11" s="33">
-        <v>1567</v>
-      </c>
-      <c r="E11" s="33">
-        <v>1470</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="35">
-        <v>1390</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="33">
-        <v>29671</v>
-      </c>
-      <c r="E12" s="10">
-        <v>3042</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="35">
-        <v>3042</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D7" s="14">
+        <v>3445.49</v>
+      </c>
+      <c r="E7" s="33">
+        <v>4850</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="34">
+        <v>3445.49</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="36">
+        <v>7410</v>
+      </c>
+      <c r="D8" s="14">
+        <v>5475.49</v>
+      </c>
+      <c r="E8" s="36">
+        <v>11499</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5475.49</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="33">
-        <v>3160</v>
-      </c>
-      <c r="D13" s="10">
-        <v>2030</v>
-      </c>
-      <c r="E13" s="33">
-        <v>6649</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="35">
-        <v>2030</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="33">
-        <v>4250</v>
-      </c>
-      <c r="D14" s="33">
-        <v>3445.49</v>
-      </c>
-      <c r="E14" s="10">
-        <v>2910</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="35">
-        <v>2910</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="10">
-        <v>25443</v>
-      </c>
-      <c r="D15" s="37">
-        <v>52362.49</v>
-      </c>
-      <c r="E15" s="37">
-        <v>26889.5</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="10">
-        <v>22190.5</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2047,7 +1575,7 @@
   <sheetData>
     <row r="2" ht="34" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
@@ -2056,132 +1584,132 @@
       <c r="G2" s="30"/>
     </row>
     <row r="4" ht="36" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
+      <c r="B4" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="B5" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="7" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
+      <c r="B7" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
     </row>
     <row r="8" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
     </row>
     <row r="10" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>118</v>
+      <c r="C10" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="42">
+        <v>2340</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="43">
-        <v>3039</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="49">
-        <v>3042</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="F12" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>125</v>
+      <c r="C12" s="48">
+        <v>3118</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="49">
-        <v>3040</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="G13" s="53" t="s">
-        <v>127</v>
+      <c r="B13" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="48">
+        <v>3335</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
+      <c r="B15" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
